--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,14 +754,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45163.60947177998</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -783,8 +779,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -799,22 +793,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="15">
       <c r="A29" s="10" t="inlineStr">
         <is>
@@ -846,10 +824,8 @@
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>261,855$</t>
-        </is>
+      <c r="D30" s="8" t="n">
+        <v>1507.207</v>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -857,7 +833,6 @@
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -866,11 +841,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="B30:C30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,7 +754,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45237</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,7 +754,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,7 +754,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>

--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,10 +754,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45266</v>
+        <v>45261.57776582459</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -779,6 +783,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -793,6 +799,22 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="15">
       <c r="A29" s="10" t="inlineStr">
         <is>
@@ -824,8 +846,10 @@
         </is>
       </c>
       <c r="C30" s="20" t="n"/>
-      <c r="D30" s="8" t="n">
-        <v>1507.207</v>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>261,855$</t>
+        </is>
       </c>
       <c r="E30" s="3" t="n"/>
     </row>
@@ -833,6 +857,7 @@
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -841,11 +866,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A11:D11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
+++ b/LISTAS/ma/TEJIDO MOSQUITERO.xlsx
@@ -754,14 +754,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="14" t="n">
-        <v>45261.57776582459</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="6" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="15">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -783,8 +779,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11" ht="41.25" customHeight="1" s="15">
       <c r="A11" s="16" t="inlineStr">
         <is>
@@ -799,22 +793,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="18" customHeight="1" s="15">
       <c r="A29" s="10" t="inlineStr">
         <is>
@@ -848,7 +826,7 @@
       <c r="C30" s="20" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>261,855$</t>
+          <t>********</t>
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
@@ -857,7 +835,6 @@
     <row r="32" ht="18" customHeight="1" s="15">
       <c r="E32" s="3" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="15.75" customHeight="1" s="15">
       <c r="A34" s="4" t="n"/>
     </row>
@@ -866,11 +843,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
